--- a/补签流程_补签统计.xlsx
+++ b/补签流程_补签统计.xlsx
@@ -442,7 +442,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>生成时间：2026-10-21 13:22</t>
+          <t>生成时间：2026-10-21 13:47</t>
         </is>
       </c>
     </row>
@@ -690,35 +690,35 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>亚特兰大2号仓(SN)</t>
+          <t>亚特兰大5号仓</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2950</v>
+        <v>3414</v>
       </c>
       <c r="E4" t="n">
-        <v>257</v>
+        <v>91</v>
       </c>
       <c r="F4" t="n">
-        <v>8.699999999999999</v>
+        <v>2.7</v>
       </c>
       <c r="G4" t="n">
         <v>100</v>
       </c>
       <c r="H4" t="n">
-        <v>2724</v>
+        <v>3140</v>
       </c>
       <c r="I4" t="n">
-        <v>282</v>
+        <v>182</v>
       </c>
       <c r="J4" t="n">
-        <v>10.4</v>
+        <v>5.8</v>
       </c>
       <c r="K4" t="n">
         <v>100</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.6</v>
+        <v>-3.1</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -737,35 +737,35 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>亚特兰大5号仓</t>
+          <t>亚特兰大2号仓(SN)</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3414</v>
+        <v>2950</v>
       </c>
       <c r="E5" t="n">
-        <v>91</v>
+        <v>257</v>
       </c>
       <c r="F5" t="n">
-        <v>2.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="G5" t="n">
         <v>100</v>
       </c>
       <c r="H5" t="n">
-        <v>3140</v>
+        <v>2724</v>
       </c>
       <c r="I5" t="n">
-        <v>182</v>
+        <v>282</v>
       </c>
       <c r="J5" t="n">
-        <v>5.8</v>
+        <v>10.4</v>
       </c>
       <c r="K5" t="n">
         <v>100</v>
       </c>
       <c r="L5" t="n">
-        <v>-3.1</v>
+        <v>-1.6</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -972,35 +972,35 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>洛杉矶28号仓</t>
+          <t>洛杉矶7号仓</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2024</v>
+        <v>5810</v>
       </c>
       <c r="E10" t="n">
-        <v>45</v>
+        <v>164</v>
       </c>
       <c r="F10" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="G10" t="n">
         <v>100</v>
       </c>
       <c r="H10" t="n">
-        <v>1792</v>
+        <v>4472</v>
       </c>
       <c r="I10" t="n">
-        <v>43</v>
+        <v>119</v>
       </c>
       <c r="J10" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="K10" t="n">
         <v>100</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.2</v>
+        <v>0.2</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1019,39 +1019,27 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>洛杉矶18号仓</t>
+          <t>洛杉矶26号仓（SN)</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1982</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>23</v>
-      </c>
-      <c r="F11" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="G11" t="n">
-        <v>100</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>1966</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>34</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="K11" t="n">
-        <v>100</v>
-      </c>
-      <c r="L11" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="M11" t="n">
         <v>0</v>
       </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1066,35 +1054,35 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>洛杉矶27号仓(PPS)</t>
+          <t>洛杉矶3号仓(中邮)</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>3454</v>
+        <v>1036</v>
       </c>
       <c r="E12" t="n">
-        <v>61</v>
+        <v>15</v>
       </c>
       <c r="F12" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="G12" t="n">
         <v>100</v>
       </c>
       <c r="H12" t="n">
-        <v>3046</v>
+        <v>1108</v>
       </c>
       <c r="I12" t="n">
-        <v>70</v>
+        <v>33</v>
       </c>
       <c r="J12" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="K12" t="n">
         <v>100</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.5</v>
+        <v>-1.5</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1113,35 +1101,35 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>洛杉矶7号仓</t>
+          <t>洛杉矶20号仓</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>5810</v>
+        <v>1398</v>
       </c>
       <c r="E13" t="n">
-        <v>164</v>
+        <v>61</v>
       </c>
       <c r="F13" t="n">
-        <v>2.8</v>
+        <v>4.4</v>
       </c>
       <c r="G13" t="n">
         <v>100</v>
       </c>
       <c r="H13" t="n">
-        <v>4472</v>
+        <v>1250</v>
       </c>
       <c r="I13" t="n">
-        <v>119</v>
+        <v>31</v>
       </c>
       <c r="J13" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="K13" t="n">
         <v>100</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2</v>
+        <v>1.9</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1160,27 +1148,39 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>洛杉矶26号仓（SN)</t>
+          <t>洛杉矶6号仓</t>
         </is>
       </c>
       <c r="D14" t="n">
+        <v>2124</v>
+      </c>
+      <c r="E14" t="n">
+        <v>30</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G14" t="n">
+        <v>100</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1996</v>
+      </c>
+      <c r="I14" t="n">
+        <v>29</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K14" t="n">
+        <v>100</v>
+      </c>
+      <c r="L14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="M14" t="n">
         <v>0</v>
       </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>洛杉矶12号仓</t>
+          <t>洛杉矶23号仓</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1230,27 +1230,39 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>洛杉矶23号仓</t>
+          <t>洛杉矶1号仓(SN)</t>
         </is>
       </c>
       <c r="D16" t="n">
+        <v>3102</v>
+      </c>
+      <c r="E16" t="n">
+        <v>76</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G16" t="n">
+        <v>100</v>
+      </c>
+      <c r="H16" t="n">
+        <v>3084</v>
+      </c>
+      <c r="I16" t="n">
+        <v>150</v>
+      </c>
+      <c r="J16" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K16" t="n">
+        <v>100</v>
+      </c>
+      <c r="L16" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="M16" t="n">
         <v>0</v>
       </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1265,35 +1277,35 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>洛杉矶2号仓(GDV)</t>
+          <t>洛杉矶19号仓(TT)</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>624</v>
+        <v>14186</v>
       </c>
       <c r="E17" t="n">
-        <v>9</v>
+        <v>546</v>
       </c>
       <c r="F17" t="n">
-        <v>1.4</v>
+        <v>3.8</v>
       </c>
       <c r="G17" t="n">
         <v>100</v>
       </c>
       <c r="H17" t="n">
-        <v>576</v>
+        <v>12200</v>
       </c>
       <c r="I17" t="n">
-        <v>16</v>
+        <v>438</v>
       </c>
       <c r="J17" t="n">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="K17" t="n">
         <v>100</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.3</v>
+        <v>0.3</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -1312,35 +1324,35 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>洛杉矶19号仓(TT)</t>
+          <t>洛杉矶28号仓</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14186</v>
+        <v>2024</v>
       </c>
       <c r="E18" t="n">
-        <v>546</v>
+        <v>45</v>
       </c>
       <c r="F18" t="n">
-        <v>3.8</v>
+        <v>2.2</v>
       </c>
       <c r="G18" t="n">
         <v>100</v>
       </c>
       <c r="H18" t="n">
-        <v>12200</v>
+        <v>1792</v>
       </c>
       <c r="I18" t="n">
-        <v>438</v>
+        <v>43</v>
       </c>
       <c r="J18" t="n">
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
       <c r="K18" t="n">
         <v>100</v>
       </c>
       <c r="L18" t="n">
-        <v>0.3</v>
+        <v>-0.2</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -1359,35 +1371,35 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>洛杉矶20号仓</t>
+          <t>洛杉矶21号仓</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1398</v>
+        <v>3994</v>
       </c>
       <c r="E19" t="n">
-        <v>61</v>
+        <v>87</v>
       </c>
       <c r="F19" t="n">
-        <v>4.4</v>
+        <v>2.2</v>
       </c>
       <c r="G19" t="n">
         <v>100</v>
       </c>
       <c r="H19" t="n">
-        <v>1250</v>
+        <v>3558</v>
       </c>
       <c r="I19" t="n">
-        <v>31</v>
+        <v>93</v>
       </c>
       <c r="J19" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="K19" t="n">
         <v>100</v>
       </c>
       <c r="L19" t="n">
-        <v>1.9</v>
+        <v>-0.4</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -1406,35 +1418,35 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>洛杉矶21号仓</t>
+          <t>洛杉矶2号仓(GDV)</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>3994</v>
+        <v>624</v>
       </c>
       <c r="E20" t="n">
-        <v>87</v>
+        <v>9</v>
       </c>
       <c r="F20" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="G20" t="n">
         <v>100</v>
       </c>
       <c r="H20" t="n">
-        <v>3558</v>
+        <v>576</v>
       </c>
       <c r="I20" t="n">
-        <v>93</v>
+        <v>16</v>
       </c>
       <c r="J20" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="K20" t="n">
         <v>100</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.4</v>
+        <v>-1.3</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -1453,39 +1465,27 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>洛杉矶10号仓</t>
+          <t>洛杉矶12号仓</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1112</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>16</v>
-      </c>
-      <c r="F21" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="G21" t="n">
-        <v>100</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>976</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>9</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="K21" t="n">
-        <v>100</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M21" t="n">
         <v>0</v>
       </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1500,35 +1500,35 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>洛杉矶6号仓</t>
+          <t>洛杉矶5号仓</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>2124</v>
+        <v>1380</v>
       </c>
       <c r="E22" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F22" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="G22" t="n">
         <v>100</v>
       </c>
       <c r="H22" t="n">
-        <v>1996</v>
+        <v>1282</v>
       </c>
       <c r="I22" t="n">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="J22" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="K22" t="n">
         <v>100</v>
       </c>
       <c r="L22" t="n">
-        <v>-0</v>
+        <v>-1.4</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -1547,35 +1547,35 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>洛杉矶25号仓</t>
+          <t>洛杉矶18号仓</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>4324</v>
+        <v>1982</v>
       </c>
       <c r="E23" t="n">
-        <v>91</v>
+        <v>23</v>
       </c>
       <c r="F23" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="G23" t="n">
         <v>100</v>
       </c>
       <c r="H23" t="n">
-        <v>3904</v>
+        <v>1966</v>
       </c>
       <c r="I23" t="n">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="J23" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="K23" t="n">
         <v>100</v>
       </c>
       <c r="L23" t="n">
-        <v>0.7</v>
+        <v>-0.6</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -1594,35 +1594,35 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>洛杉矶1号仓(SN)</t>
+          <t>洛杉矶25号仓</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>3102</v>
+        <v>4324</v>
       </c>
       <c r="E24" t="n">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="F24" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="G24" t="n">
         <v>100</v>
       </c>
       <c r="H24" t="n">
-        <v>3084</v>
+        <v>3904</v>
       </c>
       <c r="I24" t="n">
-        <v>150</v>
+        <v>56</v>
       </c>
       <c r="J24" t="n">
-        <v>4.9</v>
+        <v>1.4</v>
       </c>
       <c r="K24" t="n">
         <v>100</v>
       </c>
       <c r="L24" t="n">
-        <v>-2.4</v>
+        <v>0.7</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -1641,26 +1641,26 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>洛杉矶17号仓</t>
+          <t>洛杉矶27号仓(PPS)</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>2252</v>
+        <v>3454</v>
       </c>
       <c r="E25" t="n">
         <v>61</v>
       </c>
       <c r="F25" t="n">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="G25" t="n">
         <v>100</v>
       </c>
       <c r="H25" t="n">
-        <v>1954</v>
+        <v>3046</v>
       </c>
       <c r="I25" t="n">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="J25" t="n">
         <v>2.3</v>
@@ -1669,7 +1669,7 @@
         <v>100</v>
       </c>
       <c r="L25" t="n">
-        <v>0.5</v>
+        <v>-0.5</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -1688,14 +1688,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>洛杉矶3号仓(中邮)</t>
+          <t>洛杉矶10号仓</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1036</v>
+        <v>1112</v>
       </c>
       <c r="E26" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F26" t="n">
         <v>1.4</v>
@@ -1704,19 +1704,19 @@
         <v>100</v>
       </c>
       <c r="H26" t="n">
-        <v>1108</v>
+        <v>976</v>
       </c>
       <c r="I26" t="n">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="J26" t="n">
-        <v>3</v>
+        <v>0.9</v>
       </c>
       <c r="K26" t="n">
         <v>100</v>
       </c>
       <c r="L26" t="n">
-        <v>-1.5</v>
+        <v>0.5</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -1735,35 +1735,35 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>洛杉矶5号仓</t>
+          <t>洛杉矶17号仓</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1380</v>
+        <v>2252</v>
       </c>
       <c r="E27" t="n">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="F27" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="G27" t="n">
         <v>100</v>
       </c>
       <c r="H27" t="n">
-        <v>1282</v>
+        <v>1954</v>
       </c>
       <c r="I27" t="n">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="J27" t="n">
-        <v>4</v>
+        <v>2.3</v>
       </c>
       <c r="K27" t="n">
         <v>100</v>
       </c>
       <c r="L27" t="n">
-        <v>-1.4</v>
+        <v>0.5</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -1782,35 +1782,35 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>多伦多3号仓</t>
+          <t>温哥华2号仓</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>574</v>
+        <v>170</v>
       </c>
       <c r="E28" t="n">
         <v>3</v>
       </c>
       <c r="F28" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="G28" t="n">
         <v>100</v>
       </c>
       <c r="H28" t="n">
-        <v>482</v>
+        <v>174</v>
       </c>
       <c r="I28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J28" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="K28" t="n">
         <v>100</v>
       </c>
       <c r="L28" t="n">
-        <v>0.1</v>
+        <v>1.2</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -1829,29 +1829,29 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>多伦多2号仓</t>
+          <t>多伦多3号仓</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1010</v>
+        <v>574</v>
       </c>
       <c r="E29" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="F29" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="G29" t="n">
         <v>100</v>
       </c>
       <c r="H29" t="n">
-        <v>942</v>
+        <v>482</v>
       </c>
       <c r="I29" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="J29" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="K29" t="n">
         <v>100</v>
@@ -1876,38 +1876,38 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>多伦多7号仓</t>
+          <t>多伦多2号仓</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>924</v>
+        <v>1010</v>
       </c>
       <c r="E30" t="n">
-        <v>95</v>
+        <v>14</v>
       </c>
       <c r="F30" t="n">
-        <v>10.3</v>
+        <v>1.4</v>
       </c>
       <c r="G30" t="n">
-        <v>99.8</v>
+        <v>100</v>
       </c>
       <c r="H30" t="n">
-        <v>772</v>
+        <v>942</v>
       </c>
       <c r="I30" t="n">
-        <v>103</v>
+        <v>12</v>
       </c>
       <c r="J30" t="n">
-        <v>13.3</v>
+        <v>1.3</v>
       </c>
       <c r="K30" t="n">
         <v>100</v>
       </c>
       <c r="L30" t="n">
-        <v>-3.1</v>
+        <v>0.1</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -1970,38 +1970,38 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>温哥华2号仓</t>
+          <t>多伦多7号仓</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>170</v>
+        <v>924</v>
       </c>
       <c r="E32" t="n">
-        <v>3</v>
+        <v>95</v>
       </c>
       <c r="F32" t="n">
-        <v>1.8</v>
+        <v>10.3</v>
       </c>
       <c r="G32" t="n">
-        <v>100</v>
+        <v>99.8</v>
       </c>
       <c r="H32" t="n">
-        <v>174</v>
+        <v>772</v>
       </c>
       <c r="I32" t="n">
-        <v>1</v>
+        <v>103</v>
       </c>
       <c r="J32" t="n">
-        <v>0.6</v>
+        <v>13.3</v>
       </c>
       <c r="K32" t="n">
         <v>100</v>
       </c>
       <c r="L32" t="n">
-        <v>1.2</v>
+        <v>-3.1</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="33">
@@ -2064,35 +2064,35 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>新泽西22号仓（SN）</t>
+          <t>新泽西2号仓(G3)</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1506</v>
+        <v>196</v>
       </c>
       <c r="E34" t="n">
-        <v>87</v>
+        <v>2</v>
       </c>
       <c r="F34" t="n">
-        <v>5.8</v>
+        <v>1</v>
       </c>
       <c r="G34" t="n">
         <v>100</v>
       </c>
       <c r="H34" t="n">
-        <v>1852</v>
+        <v>224</v>
       </c>
       <c r="I34" t="n">
-        <v>45</v>
+        <v>3</v>
       </c>
       <c r="J34" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="K34" t="n">
         <v>100</v>
       </c>
       <c r="L34" t="n">
-        <v>3.3</v>
+        <v>-0.3</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
@@ -2111,35 +2111,35 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>新泽西3号仓(SN)</t>
+          <t>新泽西10号仓</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>3994</v>
+        <v>7398</v>
       </c>
       <c r="E35" t="n">
-        <v>70</v>
+        <v>184</v>
       </c>
       <c r="F35" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="G35" t="n">
         <v>100</v>
       </c>
       <c r="H35" t="n">
-        <v>3314</v>
+        <v>6232</v>
       </c>
       <c r="I35" t="n">
-        <v>40</v>
+        <v>152</v>
       </c>
       <c r="J35" t="n">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="K35" t="n">
         <v>100</v>
       </c>
       <c r="L35" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
@@ -2158,35 +2158,35 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>新泽西5号仓</t>
+          <t>新泽西15号仓</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1576</v>
+        <v>3248</v>
       </c>
       <c r="E36" t="n">
-        <v>170</v>
+        <v>92</v>
       </c>
       <c r="F36" t="n">
-        <v>10.8</v>
+        <v>2.8</v>
       </c>
       <c r="G36" t="n">
         <v>100</v>
       </c>
       <c r="H36" t="n">
-        <v>1532</v>
+        <v>2904</v>
       </c>
       <c r="I36" t="n">
-        <v>118</v>
+        <v>90</v>
       </c>
       <c r="J36" t="n">
-        <v>7.7</v>
+        <v>3.1</v>
       </c>
       <c r="K36" t="n">
         <v>100</v>
       </c>
       <c r="L36" t="n">
-        <v>3.1</v>
+        <v>-0.3</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
@@ -2205,35 +2205,35 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>新泽西1号仓</t>
+          <t>新泽西18号仓</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1832</v>
+        <v>3496</v>
       </c>
       <c r="E37" t="n">
-        <v>34</v>
+        <v>175</v>
       </c>
       <c r="F37" t="n">
-        <v>1.9</v>
+        <v>5</v>
       </c>
       <c r="G37" t="n">
         <v>100</v>
       </c>
       <c r="H37" t="n">
-        <v>1904</v>
+        <v>3236</v>
       </c>
       <c r="I37" t="n">
-        <v>46</v>
+        <v>158</v>
       </c>
       <c r="J37" t="n">
-        <v>2.4</v>
+        <v>4.9</v>
       </c>
       <c r="K37" t="n">
         <v>100</v>
       </c>
       <c r="L37" t="n">
-        <v>-0.6</v>
+        <v>0.1</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
@@ -2299,35 +2299,35 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>新泽西15号仓</t>
+          <t>新泽西22号仓（SN）</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>3248</v>
+        <v>1506</v>
       </c>
       <c r="E39" t="n">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="F39" t="n">
-        <v>2.8</v>
+        <v>5.8</v>
       </c>
       <c r="G39" t="n">
         <v>100</v>
       </c>
       <c r="H39" t="n">
-        <v>2904</v>
+        <v>1852</v>
       </c>
       <c r="I39" t="n">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="J39" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="K39" t="n">
         <v>100</v>
       </c>
       <c r="L39" t="n">
-        <v>-0.3</v>
+        <v>3.3</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
@@ -2346,35 +2346,35 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>新泽西12号仓</t>
+          <t>新泽西3号仓(SN)</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>2522</v>
+        <v>3994</v>
       </c>
       <c r="E40" t="n">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="F40" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="G40" t="n">
         <v>100</v>
       </c>
       <c r="H40" t="n">
-        <v>2158</v>
+        <v>3314</v>
       </c>
       <c r="I40" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J40" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="K40" t="n">
         <v>100</v>
       </c>
       <c r="L40" t="n">
-        <v>-0.2</v>
+        <v>0.5</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
@@ -2393,35 +2393,35 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>新泽西6号仓(中邮)</t>
+          <t>新泽西12号仓</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1638</v>
+        <v>2522</v>
       </c>
       <c r="E41" t="n">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="F41" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="G41" t="n">
         <v>100</v>
       </c>
       <c r="H41" t="n">
-        <v>1552</v>
+        <v>2158</v>
       </c>
       <c r="I41" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="J41" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="K41" t="n">
         <v>100</v>
       </c>
       <c r="L41" t="n">
-        <v>-0.7</v>
+        <v>-0.2</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
@@ -2440,29 +2440,29 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>新泽西23号仓</t>
+          <t>新泽西11号仓</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>3478</v>
+        <v>3772</v>
       </c>
       <c r="E42" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="F42" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="G42" t="n">
         <v>100</v>
       </c>
       <c r="H42" t="n">
-        <v>2998</v>
+        <v>2808</v>
       </c>
       <c r="I42" t="n">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="J42" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="K42" t="n">
         <v>100</v>
@@ -2487,35 +2487,35 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>新泽西18号仓</t>
+          <t>新泽西1号仓</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>3496</v>
+        <v>1832</v>
       </c>
       <c r="E43" t="n">
-        <v>175</v>
+        <v>34</v>
       </c>
       <c r="F43" t="n">
-        <v>5</v>
+        <v>1.9</v>
       </c>
       <c r="G43" t="n">
         <v>100</v>
       </c>
       <c r="H43" t="n">
-        <v>3236</v>
+        <v>1904</v>
       </c>
       <c r="I43" t="n">
-        <v>158</v>
+        <v>46</v>
       </c>
       <c r="J43" t="n">
-        <v>4.9</v>
+        <v>2.4</v>
       </c>
       <c r="K43" t="n">
         <v>100</v>
       </c>
       <c r="L43" t="n">
-        <v>0.1</v>
+        <v>-0.6</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
@@ -2534,35 +2534,35 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>新泽西10号仓</t>
+          <t>新泽西6号仓(中邮)</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>7398</v>
+        <v>1638</v>
       </c>
       <c r="E44" t="n">
-        <v>184</v>
+        <v>17</v>
       </c>
       <c r="F44" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="G44" t="n">
         <v>100</v>
       </c>
       <c r="H44" t="n">
-        <v>6232</v>
+        <v>1552</v>
       </c>
       <c r="I44" t="n">
-        <v>152</v>
+        <v>27</v>
       </c>
       <c r="J44" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="K44" t="n">
         <v>100</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>-0.7</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
@@ -2581,35 +2581,35 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>新泽西16号仓</t>
+          <t>新泽西19号仓</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>602</v>
+        <v>1256</v>
       </c>
       <c r="E45" t="n">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="F45" t="n">
-        <v>4.2</v>
+        <v>5.6</v>
       </c>
       <c r="G45" t="n">
         <v>100</v>
       </c>
       <c r="H45" t="n">
-        <v>568</v>
+        <v>1186</v>
       </c>
       <c r="I45" t="n">
-        <v>15</v>
+        <v>69</v>
       </c>
       <c r="J45" t="n">
-        <v>2.6</v>
+        <v>5.8</v>
       </c>
       <c r="K45" t="n">
         <v>100</v>
       </c>
       <c r="L45" t="n">
-        <v>1.5</v>
+        <v>-0.2</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
@@ -2675,35 +2675,35 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>新泽西7号仓（福和乐）</t>
+          <t>新泽西23号仓</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>880</v>
+        <v>3478</v>
       </c>
       <c r="E47" t="n">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="F47" t="n">
-        <v>4.5</v>
+        <v>2.3</v>
       </c>
       <c r="G47" t="n">
         <v>100</v>
       </c>
       <c r="H47" t="n">
-        <v>746</v>
+        <v>2998</v>
       </c>
       <c r="I47" t="n">
-        <v>26</v>
+        <v>107</v>
       </c>
       <c r="J47" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K47" t="n">
         <v>100</v>
       </c>
       <c r="L47" t="n">
-        <v>1.1</v>
+        <v>-1.3</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
@@ -2722,35 +2722,35 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>新泽西8号仓</t>
+          <t>新泽西16号仓</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>3244</v>
+        <v>602</v>
       </c>
       <c r="E48" t="n">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="F48" t="n">
-        <v>2.3</v>
+        <v>4.2</v>
       </c>
       <c r="G48" t="n">
         <v>100</v>
       </c>
       <c r="H48" t="n">
-        <v>2902</v>
+        <v>568</v>
       </c>
       <c r="I48" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="J48" t="n">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="K48" t="n">
         <v>100</v>
       </c>
       <c r="L48" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="M48" t="n">
         <v>0</v>
@@ -2816,35 +2816,35 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>新泽西11号仓</t>
+          <t>新泽西5号仓</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>3772</v>
+        <v>1576</v>
       </c>
       <c r="E50" t="n">
-        <v>83</v>
+        <v>170</v>
       </c>
       <c r="F50" t="n">
-        <v>2.2</v>
+        <v>10.8</v>
       </c>
       <c r="G50" t="n">
         <v>100</v>
       </c>
       <c r="H50" t="n">
-        <v>2808</v>
+        <v>1532</v>
       </c>
       <c r="I50" t="n">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="J50" t="n">
-        <v>3.5</v>
+        <v>7.7</v>
       </c>
       <c r="K50" t="n">
         <v>100</v>
       </c>
       <c r="L50" t="n">
-        <v>-1.3</v>
+        <v>3.1</v>
       </c>
       <c r="M50" t="n">
         <v>0</v>
@@ -2863,35 +2863,35 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>新泽西2号仓(G3)</t>
+          <t>新泽西8号仓</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>196</v>
+        <v>3244</v>
       </c>
       <c r="E51" t="n">
-        <v>2</v>
+        <v>74</v>
       </c>
       <c r="F51" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="G51" t="n">
         <v>100</v>
       </c>
       <c r="H51" t="n">
-        <v>224</v>
+        <v>2902</v>
       </c>
       <c r="I51" t="n">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="J51" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="K51" t="n">
         <v>100</v>
       </c>
       <c r="L51" t="n">
-        <v>-0.3</v>
+        <v>0.7</v>
       </c>
       <c r="M51" t="n">
         <v>0</v>
@@ -2910,35 +2910,35 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>新泽西19号仓</t>
+          <t>新泽西7号仓（福和乐）</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1256</v>
+        <v>880</v>
       </c>
       <c r="E52" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="F52" t="n">
-        <v>5.6</v>
+        <v>4.5</v>
       </c>
       <c r="G52" t="n">
         <v>100</v>
       </c>
       <c r="H52" t="n">
-        <v>1186</v>
+        <v>746</v>
       </c>
       <c r="I52" t="n">
-        <v>69</v>
+        <v>26</v>
       </c>
       <c r="J52" t="n">
-        <v>5.8</v>
+        <v>3.5</v>
       </c>
       <c r="K52" t="n">
         <v>100</v>
       </c>
       <c r="L52" t="n">
-        <v>-0.2</v>
+        <v>1.1</v>
       </c>
       <c r="M52" t="n">
         <v>0</v>
@@ -2992,38 +2992,38 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>芝加哥2号仓</t>
+          <t>芝加哥5号仓</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>502</v>
+        <v>5948</v>
       </c>
       <c r="E54" t="n">
-        <v>199</v>
+        <v>715</v>
       </c>
       <c r="F54" t="n">
-        <v>39.6</v>
+        <v>12</v>
       </c>
       <c r="G54" t="n">
         <v>100</v>
       </c>
       <c r="H54" t="n">
-        <v>618</v>
+        <v>6118</v>
       </c>
       <c r="I54" t="n">
-        <v>308</v>
+        <v>809</v>
       </c>
       <c r="J54" t="n">
-        <v>49.8</v>
+        <v>13.2</v>
       </c>
       <c r="K54" t="n">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="L54" t="n">
-        <v>-10.2</v>
+        <v>-1.2</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="55">
@@ -3039,38 +3039,38 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>芝加哥5号仓</t>
+          <t>芝加哥2号仓</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>5948</v>
+        <v>502</v>
       </c>
       <c r="E55" t="n">
-        <v>715</v>
+        <v>199</v>
       </c>
       <c r="F55" t="n">
-        <v>12</v>
+        <v>39.6</v>
       </c>
       <c r="G55" t="n">
         <v>100</v>
       </c>
       <c r="H55" t="n">
-        <v>6118</v>
+        <v>618</v>
       </c>
       <c r="I55" t="n">
-        <v>809</v>
+        <v>308</v>
       </c>
       <c r="J55" t="n">
-        <v>13.2</v>
+        <v>49.8</v>
       </c>
       <c r="K55" t="n">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="L55" t="n">
-        <v>-1.2</v>
+        <v>-10.2</v>
       </c>
       <c r="M55" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3368,35 +3368,35 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>杜塞尔多夫11号仓</t>
+          <t>杜塞尔多夫16号仓</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>5670</v>
+        <v>4212</v>
       </c>
       <c r="E62" t="n">
-        <v>1923</v>
+        <v>674</v>
       </c>
       <c r="F62" t="n">
-        <v>33.9</v>
+        <v>16</v>
       </c>
       <c r="G62" t="n">
         <v>100</v>
       </c>
       <c r="H62" t="n">
-        <v>5492</v>
+        <v>4234</v>
       </c>
       <c r="I62" t="n">
-        <v>3803</v>
+        <v>1147</v>
       </c>
       <c r="J62" t="n">
-        <v>69.2</v>
+        <v>27.1</v>
       </c>
       <c r="K62" t="n">
         <v>100</v>
       </c>
       <c r="L62" t="n">
-        <v>-35.3</v>
+        <v>-11.1</v>
       </c>
       <c r="M62" t="n">
         <v>0</v>
@@ -3415,35 +3415,35 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>杜塞尔多夫3号仓</t>
+          <t>杜塞尔多夫11号仓</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>5022</v>
+        <v>5670</v>
       </c>
       <c r="E63" t="n">
-        <v>1340</v>
+        <v>1923</v>
       </c>
       <c r="F63" t="n">
-        <v>26.7</v>
+        <v>33.9</v>
       </c>
       <c r="G63" t="n">
         <v>100</v>
       </c>
       <c r="H63" t="n">
-        <v>4362</v>
+        <v>5492</v>
       </c>
       <c r="I63" t="n">
-        <v>1189</v>
+        <v>3803</v>
       </c>
       <c r="J63" t="n">
-        <v>27.3</v>
+        <v>69.2</v>
       </c>
       <c r="K63" t="n">
         <v>100</v>
       </c>
       <c r="L63" t="n">
-        <v>-0.6</v>
+        <v>-35.3</v>
       </c>
       <c r="M63" t="n">
         <v>0</v>
@@ -3509,35 +3509,35 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>杜塞尔多夫12号仓</t>
+          <t>杜塞尔多夫3号仓</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>10480</v>
+        <v>5022</v>
       </c>
       <c r="E65" t="n">
-        <v>2263</v>
+        <v>1340</v>
       </c>
       <c r="F65" t="n">
-        <v>21.6</v>
+        <v>26.7</v>
       </c>
       <c r="G65" t="n">
         <v>100</v>
       </c>
       <c r="H65" t="n">
-        <v>11326</v>
+        <v>4362</v>
       </c>
       <c r="I65" t="n">
-        <v>2702</v>
+        <v>1189</v>
       </c>
       <c r="J65" t="n">
-        <v>23.9</v>
+        <v>27.3</v>
       </c>
       <c r="K65" t="n">
         <v>100</v>
       </c>
       <c r="L65" t="n">
-        <v>-2.3</v>
+        <v>-0.6</v>
       </c>
       <c r="M65" t="n">
         <v>0</v>
@@ -3603,35 +3603,35 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>杜塞尔多夫16号仓</t>
+          <t>杜塞尔多夫6号仓</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>4212</v>
+        <v>4250</v>
       </c>
       <c r="E67" t="n">
-        <v>674</v>
+        <v>1688</v>
       </c>
       <c r="F67" t="n">
-        <v>16</v>
+        <v>39.7</v>
       </c>
       <c r="G67" t="n">
         <v>100</v>
       </c>
       <c r="H67" t="n">
-        <v>4234</v>
+        <v>3456</v>
       </c>
       <c r="I67" t="n">
-        <v>1147</v>
+        <v>1325</v>
       </c>
       <c r="J67" t="n">
-        <v>27.1</v>
+        <v>38.3</v>
       </c>
       <c r="K67" t="n">
         <v>100</v>
       </c>
       <c r="L67" t="n">
-        <v>-11.1</v>
+        <v>1.4</v>
       </c>
       <c r="M67" t="n">
         <v>0</v>
@@ -3685,35 +3685,35 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>杜塞尔多夫6号仓</t>
+          <t>杜塞尔多夫10号仓</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>4250</v>
+        <v>3926</v>
       </c>
       <c r="E69" t="n">
-        <v>1688</v>
+        <v>1768</v>
       </c>
       <c r="F69" t="n">
-        <v>39.7</v>
+        <v>45</v>
       </c>
       <c r="G69" t="n">
         <v>100</v>
       </c>
       <c r="H69" t="n">
-        <v>3456</v>
+        <v>3562</v>
       </c>
       <c r="I69" t="n">
-        <v>1325</v>
+        <v>1482</v>
       </c>
       <c r="J69" t="n">
-        <v>38.3</v>
+        <v>41.6</v>
       </c>
       <c r="K69" t="n">
         <v>100</v>
       </c>
       <c r="L69" t="n">
-        <v>1.4</v>
+        <v>3.4</v>
       </c>
       <c r="M69" t="n">
         <v>0</v>
@@ -3779,35 +3779,35 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>杜塞尔多夫10号仓</t>
+          <t>杜塞尔多夫12号仓</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>3926</v>
+        <v>10480</v>
       </c>
       <c r="E71" t="n">
-        <v>1768</v>
+        <v>2263</v>
       </c>
       <c r="F71" t="n">
-        <v>45</v>
+        <v>21.6</v>
       </c>
       <c r="G71" t="n">
         <v>100</v>
       </c>
       <c r="H71" t="n">
-        <v>3562</v>
+        <v>11326</v>
       </c>
       <c r="I71" t="n">
-        <v>1482</v>
+        <v>2702</v>
       </c>
       <c r="J71" t="n">
-        <v>41.6</v>
+        <v>23.9</v>
       </c>
       <c r="K71" t="n">
         <v>100</v>
       </c>
       <c r="L71" t="n">
-        <v>3.4</v>
+        <v>-2.3</v>
       </c>
       <c r="M71" t="n">
         <v>0</v>
@@ -3826,31 +3826,39 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>布拉格4号仓</t>
+          <t>布拉格3号仓</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>0</v>
+        <v>1002</v>
       </c>
       <c r="E72" t="n">
-        <v>0</v>
-      </c>
-      <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr"/>
+        <v>283</v>
+      </c>
+      <c r="F72" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="G72" t="n">
+        <v>100</v>
+      </c>
       <c r="H72" t="n">
-        <v>618</v>
+        <v>920</v>
       </c>
       <c r="I72" t="n">
-        <v>106</v>
+        <v>295</v>
       </c>
       <c r="J72" t="n">
-        <v>17.2</v>
+        <v>32.1</v>
       </c>
       <c r="K72" t="n">
         <v>100</v>
       </c>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
+      <c r="L72" t="n">
+        <v>-3.8</v>
+      </c>
+      <c r="M72" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3865,7 +3873,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>卡派组</t>
+          <t>布拉格4号仓</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -3877,13 +3885,17 @@
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="n">
-        <v>0</v>
+        <v>618</v>
       </c>
       <c r="I73" t="n">
-        <v>0</v>
-      </c>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
+        <v>106</v>
+      </c>
+      <c r="J73" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="K73" t="n">
+        <v>100</v>
+      </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr"/>
     </row>
@@ -3900,35 +3912,35 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>布拉格3号仓</t>
+          <t>布拉格2号仓</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>1002</v>
+        <v>1210</v>
       </c>
       <c r="E74" t="n">
-        <v>283</v>
+        <v>272</v>
       </c>
       <c r="F74" t="n">
-        <v>28.2</v>
+        <v>22.5</v>
       </c>
       <c r="G74" t="n">
         <v>100</v>
       </c>
       <c r="H74" t="n">
-        <v>920</v>
+        <v>890</v>
       </c>
       <c r="I74" t="n">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="J74" t="n">
-        <v>32.1</v>
+        <v>32.8</v>
       </c>
       <c r="K74" t="n">
         <v>100</v>
       </c>
       <c r="L74" t="n">
-        <v>-3.8</v>
+        <v>-10.3</v>
       </c>
       <c r="M74" t="n">
         <v>0</v>
@@ -3947,35 +3959,35 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>布拉格7号仓</t>
+          <t>布拉格8号仓</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>844</v>
+        <v>974</v>
       </c>
       <c r="E75" t="n">
-        <v>138</v>
+        <v>194</v>
       </c>
       <c r="F75" t="n">
-        <v>16.4</v>
+        <v>19.9</v>
       </c>
       <c r="G75" t="n">
         <v>100</v>
       </c>
       <c r="H75" t="n">
-        <v>750</v>
+        <v>734</v>
       </c>
       <c r="I75" t="n">
-        <v>79</v>
+        <v>121</v>
       </c>
       <c r="J75" t="n">
-        <v>10.5</v>
+        <v>16.5</v>
       </c>
       <c r="K75" t="n">
         <v>100</v>
       </c>
       <c r="L75" t="n">
-        <v>5.8</v>
+        <v>3.4</v>
       </c>
       <c r="M75" t="n">
         <v>0</v>
@@ -3994,39 +4006,27 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>布拉格2号仓</t>
+          <t>卡派组</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>1210</v>
+        <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>272</v>
-      </c>
-      <c r="F76" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="G76" t="n">
-        <v>100</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr"/>
       <c r="H76" t="n">
-        <v>890</v>
+        <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>292</v>
-      </c>
-      <c r="J76" t="n">
-        <v>32.8</v>
-      </c>
-      <c r="K76" t="n">
-        <v>100</v>
-      </c>
-      <c r="L76" t="n">
-        <v>-10.3</v>
-      </c>
-      <c r="M76" t="n">
         <v>0</v>
       </c>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4041,35 +4041,35 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>布拉格8号仓</t>
+          <t>布拉格7号仓</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>974</v>
+        <v>844</v>
       </c>
       <c r="E77" t="n">
-        <v>194</v>
+        <v>138</v>
       </c>
       <c r="F77" t="n">
-        <v>19.9</v>
+        <v>16.4</v>
       </c>
       <c r="G77" t="n">
         <v>100</v>
       </c>
       <c r="H77" t="n">
-        <v>734</v>
+        <v>750</v>
       </c>
       <c r="I77" t="n">
-        <v>121</v>
+        <v>79</v>
       </c>
       <c r="J77" t="n">
-        <v>16.5</v>
+        <v>10.5</v>
       </c>
       <c r="K77" t="n">
         <v>100</v>
       </c>
       <c r="L77" t="n">
-        <v>3.4</v>
+        <v>5.8</v>
       </c>
       <c r="M77" t="n">
         <v>0</v>
@@ -4135,39 +4135,27 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>巴黎2号仓</t>
+          <t>巴黎6号仓</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>2918</v>
+        <v>1864</v>
       </c>
       <c r="E79" t="n">
-        <v>276</v>
+        <v>513</v>
       </c>
       <c r="F79" t="n">
-        <v>9.5</v>
+        <v>27.5</v>
       </c>
       <c r="G79" t="n">
-        <v>100</v>
-      </c>
-      <c r="H79" t="n">
-        <v>2622</v>
-      </c>
-      <c r="I79" t="n">
-        <v>340</v>
-      </c>
-      <c r="J79" t="n">
-        <v>13</v>
-      </c>
-      <c r="K79" t="n">
-        <v>100</v>
-      </c>
-      <c r="L79" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="M79" t="n">
-        <v>0</v>
-      </c>
+        <v>99.8</v>
+      </c>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4182,38 +4170,38 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>巴黎5号仓</t>
+          <t>巴黎1号仓</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>2664</v>
+        <v>1056</v>
       </c>
       <c r="E80" t="n">
-        <v>1473</v>
+        <v>29</v>
       </c>
       <c r="F80" t="n">
-        <v>55.3</v>
+        <v>2.7</v>
       </c>
       <c r="G80" t="n">
-        <v>100</v>
+        <v>97.3</v>
       </c>
       <c r="H80" t="n">
-        <v>1954</v>
+        <v>1032</v>
       </c>
       <c r="I80" t="n">
-        <v>1379</v>
+        <v>317</v>
       </c>
       <c r="J80" t="n">
-        <v>70.59999999999999</v>
+        <v>30.7</v>
       </c>
       <c r="K80" t="n">
-        <v>100</v>
+        <v>95.7</v>
       </c>
       <c r="L80" t="n">
-        <v>-15.3</v>
+        <v>-28</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="81">
@@ -4229,38 +4217,38 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>巴黎1号仓</t>
+          <t>巴黎5号仓</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>1056</v>
+        <v>2664</v>
       </c>
       <c r="E81" t="n">
-        <v>29</v>
+        <v>1473</v>
       </c>
       <c r="F81" t="n">
-        <v>2.7</v>
+        <v>55.3</v>
       </c>
       <c r="G81" t="n">
-        <v>97.3</v>
+        <v>100</v>
       </c>
       <c r="H81" t="n">
-        <v>1032</v>
+        <v>1954</v>
       </c>
       <c r="I81" t="n">
-        <v>317</v>
+        <v>1379</v>
       </c>
       <c r="J81" t="n">
-        <v>30.7</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="K81" t="n">
-        <v>95.7</v>
+        <v>100</v>
       </c>
       <c r="L81" t="n">
-        <v>-28</v>
+        <v>-15.3</v>
       </c>
       <c r="M81" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -4276,27 +4264,39 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>巴黎6号仓</t>
+          <t>巴黎2号仓</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>1864</v>
+        <v>2918</v>
       </c>
       <c r="E82" t="n">
-        <v>513</v>
+        <v>276</v>
       </c>
       <c r="F82" t="n">
-        <v>27.5</v>
+        <v>9.5</v>
       </c>
       <c r="G82" t="n">
-        <v>99.8</v>
-      </c>
-      <c r="H82" t="inlineStr"/>
-      <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr"/>
+        <v>100</v>
+      </c>
+      <c r="H82" t="n">
+        <v>2622</v>
+      </c>
+      <c r="I82" t="n">
+        <v>340</v>
+      </c>
+      <c r="J82" t="n">
+        <v>13</v>
+      </c>
+      <c r="K82" t="n">
+        <v>100</v>
+      </c>
+      <c r="L82" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="M82" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -4358,39 +4358,27 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>弗罗茨瓦夫3号仓(SN)</t>
+          <t>弗罗茨瓦夫5号仓(TEMU)</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>29098</v>
+        <v>24502</v>
       </c>
       <c r="E84" t="n">
-        <v>13844</v>
+        <v>24124</v>
       </c>
       <c r="F84" t="n">
-        <v>47.6</v>
+        <v>98.5</v>
       </c>
       <c r="G84" t="n">
         <v>100</v>
       </c>
-      <c r="H84" t="n">
-        <v>26184</v>
-      </c>
-      <c r="I84" t="n">
-        <v>21847</v>
-      </c>
-      <c r="J84" t="n">
-        <v>83.40000000000001</v>
-      </c>
-      <c r="K84" t="n">
-        <v>100</v>
-      </c>
-      <c r="L84" t="n">
-        <v>-35.9</v>
-      </c>
-      <c r="M84" t="n">
-        <v>0</v>
-      </c>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -4405,7 +4393,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>弗罗茨瓦夫2号仓(SN)</t>
+          <t>斯武比采1号仓</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -4440,35 +4428,35 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>斯武比采2号仓</t>
+          <t>弗罗茨瓦夫3号仓(SN)</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>2516</v>
+        <v>29098</v>
       </c>
       <c r="E86" t="n">
-        <v>819</v>
+        <v>13844</v>
       </c>
       <c r="F86" t="n">
-        <v>32.6</v>
+        <v>47.6</v>
       </c>
       <c r="G86" t="n">
         <v>100</v>
       </c>
       <c r="H86" t="n">
-        <v>2424</v>
+        <v>26184</v>
       </c>
       <c r="I86" t="n">
-        <v>1220</v>
+        <v>21847</v>
       </c>
       <c r="J86" t="n">
-        <v>50.3</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="K86" t="n">
         <v>100</v>
       </c>
       <c r="L86" t="n">
-        <v>-17.8</v>
+        <v>-35.9</v>
       </c>
       <c r="M86" t="n">
         <v>0</v>
@@ -4487,27 +4475,39 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>弗罗茨瓦夫5号仓(TEMU)</t>
+          <t>斯武比采2号仓</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>24502</v>
+        <v>2516</v>
       </c>
       <c r="E87" t="n">
-        <v>24124</v>
+        <v>819</v>
       </c>
       <c r="F87" t="n">
-        <v>98.5</v>
+        <v>32.6</v>
       </c>
       <c r="G87" t="n">
         <v>100</v>
       </c>
-      <c r="H87" t="inlineStr"/>
-      <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr"/>
+      <c r="H87" t="n">
+        <v>2424</v>
+      </c>
+      <c r="I87" t="n">
+        <v>1220</v>
+      </c>
+      <c r="J87" t="n">
+        <v>50.3</v>
+      </c>
+      <c r="K87" t="n">
+        <v>100</v>
+      </c>
+      <c r="L87" t="n">
+        <v>-17.8</v>
+      </c>
+      <c r="M87" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -4522,7 +4522,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>斯武比采1号仓</t>
+          <t>弗罗茨瓦夫2号仓(SN)</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -4557,35 +4557,35 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>伯明翰16号仓</t>
+          <t>伯明翰7号仓(SN)</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>552</v>
+        <v>23124</v>
       </c>
       <c r="E89" t="n">
-        <v>11</v>
+        <v>605</v>
       </c>
       <c r="F89" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="G89" t="n">
         <v>100</v>
       </c>
       <c r="H89" t="n">
-        <v>596</v>
+        <v>19466</v>
       </c>
       <c r="I89" t="n">
-        <v>47</v>
+        <v>1286</v>
       </c>
       <c r="J89" t="n">
-        <v>7.9</v>
+        <v>6.6</v>
       </c>
       <c r="K89" t="n">
         <v>100</v>
       </c>
       <c r="L89" t="n">
-        <v>-5.9</v>
+        <v>-4</v>
       </c>
       <c r="M89" t="n">
         <v>0</v>
@@ -4604,35 +4604,35 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>伯明翰2号仓</t>
+          <t>伯明翰16号仓</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>4818</v>
+        <v>552</v>
       </c>
       <c r="E90" t="n">
-        <v>145</v>
+        <v>11</v>
       </c>
       <c r="F90" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G90" t="n">
         <v>100</v>
       </c>
       <c r="H90" t="n">
-        <v>4868</v>
+        <v>596</v>
       </c>
       <c r="I90" t="n">
-        <v>92</v>
+        <v>47</v>
       </c>
       <c r="J90" t="n">
-        <v>1.9</v>
+        <v>7.9</v>
       </c>
       <c r="K90" t="n">
         <v>100</v>
       </c>
       <c r="L90" t="n">
-        <v>1.1</v>
+        <v>-5.9</v>
       </c>
       <c r="M90" t="n">
         <v>0</v>
@@ -4651,35 +4651,35 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>伯明翰25号仓</t>
+          <t>伯明翰10号仓(TT)</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>6866</v>
+        <v>11260</v>
       </c>
       <c r="E91" t="n">
-        <v>284</v>
+        <v>108</v>
       </c>
       <c r="F91" t="n">
-        <v>4.1</v>
+        <v>1</v>
       </c>
       <c r="G91" t="n">
         <v>100</v>
       </c>
       <c r="H91" t="n">
-        <v>7060</v>
+        <v>10664</v>
       </c>
       <c r="I91" t="n">
-        <v>185</v>
+        <v>232</v>
       </c>
       <c r="J91" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="K91" t="n">
         <v>100</v>
       </c>
       <c r="L91" t="n">
-        <v>1.5</v>
+        <v>-1.2</v>
       </c>
       <c r="M91" t="n">
         <v>0</v>
@@ -4698,38 +4698,38 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>伯明翰20号仓</t>
+          <t>伯明翰15号仓</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>2082</v>
+        <v>1814</v>
       </c>
       <c r="E92" t="n">
-        <v>31</v>
+        <v>113</v>
       </c>
       <c r="F92" t="n">
-        <v>1.5</v>
+        <v>6.2</v>
       </c>
       <c r="G92" t="n">
         <v>100</v>
       </c>
       <c r="H92" t="n">
-        <v>1790</v>
+        <v>2012</v>
       </c>
       <c r="I92" t="n">
-        <v>14</v>
+        <v>154</v>
       </c>
       <c r="J92" t="n">
-        <v>0.8</v>
+        <v>7.7</v>
       </c>
       <c r="K92" t="n">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="L92" t="n">
-        <v>0.7</v>
+        <v>-1.4</v>
       </c>
       <c r="M92" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -4745,35 +4745,35 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>伯明翰15号仓</t>
+          <t>伯明翰2号仓</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>1814</v>
+        <v>4818</v>
       </c>
       <c r="E93" t="n">
-        <v>113</v>
+        <v>145</v>
       </c>
       <c r="F93" t="n">
-        <v>6.2</v>
+        <v>3</v>
       </c>
       <c r="G93" t="n">
         <v>100</v>
       </c>
       <c r="H93" t="n">
-        <v>2012</v>
+        <v>4868</v>
       </c>
       <c r="I93" t="n">
-        <v>154</v>
+        <v>92</v>
       </c>
       <c r="J93" t="n">
-        <v>7.7</v>
+        <v>1.9</v>
       </c>
       <c r="K93" t="n">
         <v>100</v>
       </c>
       <c r="L93" t="n">
-        <v>-1.4</v>
+        <v>1.1</v>
       </c>
       <c r="M93" t="n">
         <v>0</v>
@@ -4792,38 +4792,38 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>伯明翰7号仓(SN)</t>
+          <t>伯明翰20号仓</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>23124</v>
+        <v>2082</v>
       </c>
       <c r="E94" t="n">
-        <v>605</v>
+        <v>31</v>
       </c>
       <c r="F94" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="G94" t="n">
         <v>100</v>
       </c>
       <c r="H94" t="n">
-        <v>19466</v>
+        <v>1790</v>
       </c>
       <c r="I94" t="n">
-        <v>1286</v>
+        <v>14</v>
       </c>
       <c r="J94" t="n">
-        <v>6.6</v>
+        <v>0.8</v>
       </c>
       <c r="K94" t="n">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="L94" t="n">
-        <v>-4</v>
+        <v>0.7</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="95">
@@ -4839,35 +4839,35 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>伯明翰18号仓(SN)</t>
+          <t>伯明翰8号仓</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>19700</v>
+        <v>1134</v>
       </c>
       <c r="E95" t="n">
-        <v>979</v>
+        <v>31</v>
       </c>
       <c r="F95" t="n">
-        <v>5</v>
+        <v>2.7</v>
       </c>
       <c r="G95" t="n">
         <v>100</v>
       </c>
       <c r="H95" t="n">
-        <v>17440</v>
+        <v>1010</v>
       </c>
       <c r="I95" t="n">
-        <v>517</v>
+        <v>9</v>
       </c>
       <c r="J95" t="n">
-        <v>3</v>
+        <v>0.9</v>
       </c>
       <c r="K95" t="n">
         <v>100</v>
       </c>
       <c r="L95" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="M95" t="n">
         <v>0</v>
@@ -4886,35 +4886,35 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>伯明翰8号仓</t>
+          <t>伯明翰19号仓</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>1134</v>
+        <v>4232</v>
       </c>
       <c r="E96" t="n">
-        <v>31</v>
+        <v>85</v>
       </c>
       <c r="F96" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="G96" t="n">
         <v>100</v>
       </c>
       <c r="H96" t="n">
-        <v>1010</v>
+        <v>4208</v>
       </c>
       <c r="I96" t="n">
-        <v>9</v>
+        <v>114</v>
       </c>
       <c r="J96" t="n">
-        <v>0.9</v>
+        <v>2.7</v>
       </c>
       <c r="K96" t="n">
         <v>100</v>
       </c>
       <c r="L96" t="n">
-        <v>1.8</v>
+        <v>-0.7</v>
       </c>
       <c r="M96" t="n">
         <v>0</v>
@@ -4933,35 +4933,35 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>伯明翰19号仓</t>
+          <t>伯明翰18号仓(SN)</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>4232</v>
+        <v>19700</v>
       </c>
       <c r="E97" t="n">
-        <v>85</v>
+        <v>979</v>
       </c>
       <c r="F97" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G97" t="n">
         <v>100</v>
       </c>
       <c r="H97" t="n">
-        <v>4208</v>
+        <v>17440</v>
       </c>
       <c r="I97" t="n">
-        <v>114</v>
+        <v>517</v>
       </c>
       <c r="J97" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="K97" t="n">
         <v>100</v>
       </c>
       <c r="L97" t="n">
-        <v>-0.7</v>
+        <v>2</v>
       </c>
       <c r="M97" t="n">
         <v>0</v>
@@ -4980,35 +4980,35 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>伯明翰10号仓(TT)</t>
+          <t>伯明翰25号仓</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11260</v>
+        <v>6866</v>
       </c>
       <c r="E98" t="n">
-        <v>108</v>
+        <v>284</v>
       </c>
       <c r="F98" t="n">
-        <v>1</v>
+        <v>4.1</v>
       </c>
       <c r="G98" t="n">
         <v>100</v>
       </c>
       <c r="H98" t="n">
-        <v>10664</v>
+        <v>7060</v>
       </c>
       <c r="I98" t="n">
-        <v>232</v>
+        <v>185</v>
       </c>
       <c r="J98" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="K98" t="n">
         <v>100</v>
       </c>
       <c r="L98" t="n">
-        <v>-1.2</v>
+        <v>1.5</v>
       </c>
       <c r="M98" t="n">
         <v>0</v>
@@ -5203,14 +5203,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>悉尼2号仓</t>
+          <t>墨尔本3号仓</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>2678</v>
+        <v>772</v>
       </c>
       <c r="E103" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="F103" t="n">
         <v>0.9</v>
@@ -5219,19 +5219,19 @@
         <v>100</v>
       </c>
       <c r="H103" t="n">
-        <v>2352</v>
+        <v>714</v>
       </c>
       <c r="I103" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J103" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="K103" t="n">
         <v>100</v>
       </c>
       <c r="L103" t="n">
-        <v>0.2</v>
+        <v>-0.9</v>
       </c>
       <c r="M103" t="n">
         <v>0</v>
@@ -5250,14 +5250,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>墨尔本3号仓</t>
+          <t>悉尼2号仓</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>772</v>
+        <v>2678</v>
       </c>
       <c r="E104" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="F104" t="n">
         <v>0.9</v>
@@ -5266,19 +5266,19 @@
         <v>100</v>
       </c>
       <c r="H104" t="n">
-        <v>714</v>
+        <v>2352</v>
       </c>
       <c r="I104" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J104" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="K104" t="n">
         <v>100</v>
       </c>
       <c r="L104" t="n">
-        <v>-0.9</v>
+        <v>0.2</v>
       </c>
       <c r="M104" t="n">
         <v>0</v>
